--- a/outputs/Sorghum_flour_percentile_classification_matrix.xlsx
+++ b/outputs/Sorghum_flour_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="86">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>Yambio</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Minimal</t>
@@ -838,7 +841,7 @@
         <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J2" t="s">
         <v>74</v>
@@ -964,13 +967,13 @@
         <v>74</v>
       </c>
       <c r="AY2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -1035,7 +1038,7 @@
         <v>74</v>
       </c>
       <c r="U3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V3" t="s">
         <v>74</v>
@@ -1047,7 +1050,7 @@
         <v>74</v>
       </c>
       <c r="Y3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z3" t="s">
         <v>74</v>
@@ -1125,13 +1128,13 @@
         <v>74</v>
       </c>
       <c r="AY3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1142,139 +1145,139 @@
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
         <v>74</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N4" t="s">
         <v>74</v>
       </c>
       <c r="O4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S4" t="s">
         <v>74</v>
       </c>
       <c r="T4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X4" t="s">
         <v>74</v>
       </c>
       <c r="Y4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG4" t="s">
         <v>74</v>
       </c>
       <c r="AH4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AI4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL4" t="s">
         <v>74</v>
       </c>
       <c r="AM4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AO4" t="s">
         <v>74</v>
       </c>
       <c r="AP4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AQ4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR4" t="s">
         <v>74</v>
       </c>
       <c r="AS4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT4" t="s">
         <v>74</v>
       </c>
       <c r="AU4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV4" t="s">
         <v>74</v>
@@ -1283,16 +1286,16 @@
         <v>74</v>
       </c>
       <c r="AX4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1351,37 +1354,37 @@
         <v>74</v>
       </c>
       <c r="S5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T5" t="s">
         <v>74</v>
       </c>
       <c r="U5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W5" t="s">
         <v>74</v>
       </c>
       <c r="X5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD5" t="s">
         <v>74</v>
@@ -1417,10 +1420,10 @@
         <v>74</v>
       </c>
       <c r="AO5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ5" t="s">
         <v>74</v>
@@ -1429,13 +1432,13 @@
         <v>74</v>
       </c>
       <c r="AS5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV5" t="s">
         <v>74</v>
@@ -1444,16 +1447,16 @@
         <v>74</v>
       </c>
       <c r="AX5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1572,7 +1575,7 @@
         <v>74</v>
       </c>
       <c r="AM6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN6" t="s">
         <v>74</v>
@@ -1581,16 +1584,16 @@
         <v>74</v>
       </c>
       <c r="AP6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT6" t="s">
         <v>74</v>
@@ -1608,13 +1611,13 @@
         <v>74</v>
       </c>
       <c r="AY6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1673,22 +1676,22 @@
         <v>74</v>
       </c>
       <c r="S7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T7" t="s">
         <v>74</v>
       </c>
       <c r="U7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V7" t="s">
         <v>74</v>
       </c>
       <c r="W7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y7" t="s">
         <v>74</v>
@@ -1697,16 +1700,16 @@
         <v>74</v>
       </c>
       <c r="AA7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="s">
         <v>74</v>
       </c>
       <c r="AC7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE7" t="s">
         <v>74</v>
@@ -1715,22 +1718,22 @@
         <v>74</v>
       </c>
       <c r="AG7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="s">
         <v>74</v>
       </c>
       <c r="AK7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="s">
         <v>74</v>
@@ -1769,13 +1772,13 @@
         <v>74</v>
       </c>
       <c r="AY7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1858,10 +1861,10 @@
         <v>74</v>
       </c>
       <c r="AA8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC8" t="s">
         <v>74</v>
@@ -1930,13 +1933,13 @@
         <v>74</v>
       </c>
       <c r="AY8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -2085,19 +2088,19 @@
         <v>74</v>
       </c>
       <c r="AW9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX9" t="s">
         <v>74</v>
       </c>
       <c r="AY9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2105,22 +2108,22 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s">
         <v>74</v>
@@ -2210,55 +2213,55 @@
         <v>74</v>
       </c>
       <c r="AK10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN10" t="s">
         <v>74</v>
       </c>
       <c r="AO10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP10" t="s">
         <v>74</v>
       </c>
       <c r="AQ10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT10" t="s">
         <v>74</v>
       </c>
       <c r="AU10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AW10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2266,19 +2269,19 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
         <v>74</v>
@@ -2287,139 +2290,139 @@
         <v>74</v>
       </c>
       <c r="I11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R11" t="s">
         <v>74</v>
       </c>
       <c r="S11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X11" t="s">
         <v>74</v>
       </c>
       <c r="Y11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z11" t="s">
         <v>74</v>
       </c>
       <c r="AA11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE11" t="s">
         <v>74</v>
       </c>
       <c r="AF11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AI11" t="s">
         <v>74</v>
       </c>
       <c r="AJ11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX11" t="s">
         <v>76</v>
       </c>
-      <c r="AN11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>75</v>
-      </c>
       <c r="AY11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AZ11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BA11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2427,13 +2430,13 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
         <v>74</v>
@@ -2451,7 +2454,7 @@
         <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K12" t="s">
         <v>74</v>
@@ -2481,10 +2484,10 @@
         <v>74</v>
       </c>
       <c r="T12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V12" t="s">
         <v>74</v>
@@ -2532,13 +2535,13 @@
         <v>74</v>
       </c>
       <c r="AK12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s">
         <v>74</v>
       </c>
       <c r="AM12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="s">
         <v>74</v>
@@ -2550,10 +2553,10 @@
         <v>74</v>
       </c>
       <c r="AQ12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS12" t="s">
         <v>74</v>
@@ -2574,13 +2577,13 @@
         <v>74</v>
       </c>
       <c r="AY12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2627,7 +2630,7 @@
         <v>74</v>
       </c>
       <c r="O13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P13" t="s">
         <v>74</v>
@@ -2636,10 +2639,10 @@
         <v>74</v>
       </c>
       <c r="R13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T13" t="s">
         <v>74</v>
@@ -2660,13 +2663,13 @@
         <v>74</v>
       </c>
       <c r="Z13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC13" t="s">
         <v>74</v>
@@ -2678,22 +2681,22 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s">
         <v>74</v>
       </c>
       <c r="AK13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s">
         <v>74</v>
@@ -2708,10 +2711,10 @@
         <v>74</v>
       </c>
       <c r="AP13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AQ13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AR13" t="s">
         <v>74</v>
@@ -2720,7 +2723,7 @@
         <v>74</v>
       </c>
       <c r="AT13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU13" t="s">
         <v>74</v>
@@ -2735,13 +2738,13 @@
         <v>74</v>
       </c>
       <c r="AY13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BA13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2827,7 +2830,7 @@
         <v>74</v>
       </c>
       <c r="AB14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC14" t="s">
         <v>74</v>
@@ -2836,37 +2839,37 @@
         <v>74</v>
       </c>
       <c r="AE14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="s">
         <v>74</v>
       </c>
       <c r="AK14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AO14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP14" t="s">
         <v>74</v>
@@ -2875,7 +2878,7 @@
         <v>74</v>
       </c>
       <c r="AR14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS14" t="s">
         <v>74</v>
@@ -2884,25 +2887,25 @@
         <v>74</v>
       </c>
       <c r="AU14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV14" t="s">
         <v>74</v>
       </c>
       <c r="AW14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX14" t="s">
         <v>74</v>
       </c>
       <c r="AY14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -2955,37 +2958,37 @@
         <v>74</v>
       </c>
       <c r="Q15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X15" t="s">
         <v>74</v>
       </c>
       <c r="Y15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB15" t="s">
         <v>74</v>
@@ -2997,7 +3000,7 @@
         <v>74</v>
       </c>
       <c r="AE15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF15" t="s">
         <v>74</v>
@@ -3006,13 +3009,13 @@
         <v>74</v>
       </c>
       <c r="AH15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s">
         <v>74</v>
       </c>
       <c r="AJ15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK15" t="s">
         <v>74</v>
@@ -3021,7 +3024,7 @@
         <v>74</v>
       </c>
       <c r="AM15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN15" t="s">
         <v>74</v>
@@ -3030,10 +3033,10 @@
         <v>74</v>
       </c>
       <c r="AP15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AR15" t="s">
         <v>74</v>
@@ -3057,13 +3060,13 @@
         <v>74</v>
       </c>
       <c r="AY15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3074,10 +3077,10 @@
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
         <v>74</v>
@@ -3086,7 +3089,7 @@
         <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s">
         <v>74</v>
@@ -3143,7 +3146,7 @@
         <v>74</v>
       </c>
       <c r="Z16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA16" t="s">
         <v>74</v>
@@ -3158,25 +3161,25 @@
         <v>74</v>
       </c>
       <c r="AE16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG16" t="s">
         <v>74</v>
       </c>
       <c r="AH16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="s">
         <v>74</v>
       </c>
       <c r="AK16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="s">
         <v>74</v>
@@ -3203,28 +3206,28 @@
         <v>74</v>
       </c>
       <c r="AT16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AW16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX16" t="s">
         <v>74</v>
       </c>
       <c r="AY16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3256,10 +3259,10 @@
         <v>74</v>
       </c>
       <c r="J17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L17" t="s">
         <v>74</v>
@@ -3277,7 +3280,7 @@
         <v>74</v>
       </c>
       <c r="Q17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R17" t="s">
         <v>74</v>
@@ -3352,40 +3355,40 @@
         <v>74</v>
       </c>
       <c r="AP17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AW17" t="s">
         <v>74</v>
       </c>
       <c r="AX17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3393,19 +3396,19 @@
         <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
         <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
         <v>74</v>
@@ -3414,7 +3417,7 @@
         <v>74</v>
       </c>
       <c r="I18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J18" t="s">
         <v>74</v>
@@ -3423,25 +3426,25 @@
         <v>74</v>
       </c>
       <c r="L18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S18" t="s">
         <v>74</v>
@@ -3450,10 +3453,10 @@
         <v>74</v>
       </c>
       <c r="U18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W18" t="s">
         <v>74</v>
@@ -3462,13 +3465,13 @@
         <v>74</v>
       </c>
       <c r="Y18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z18" t="s">
         <v>74</v>
       </c>
       <c r="AA18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB18" t="s">
         <v>74</v>
@@ -3477,58 +3480,58 @@
         <v>74</v>
       </c>
       <c r="AD18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG18" t="s">
         <v>74</v>
       </c>
       <c r="AH18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="s">
         <v>74</v>
       </c>
       <c r="AK18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL18" t="s">
         <v>74</v>
       </c>
       <c r="AM18" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>75</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT18" t="s">
         <v>76</v>
       </c>
-      <c r="AN18" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO18" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP18" t="s">
-        <v>76</v>
-      </c>
-      <c r="AQ18" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR18" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS18" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT18" t="s">
-        <v>75</v>
-      </c>
       <c r="AU18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV18" t="s">
         <v>74</v>
@@ -3537,16 +3540,16 @@
         <v>74</v>
       </c>
       <c r="AX18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AZ18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3554,22 +3557,22 @@
         <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
         <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
         <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s">
         <v>74</v>
@@ -3578,16 +3581,16 @@
         <v>74</v>
       </c>
       <c r="J19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N19" t="s">
         <v>74</v>
@@ -3596,7 +3599,7 @@
         <v>74</v>
       </c>
       <c r="P19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q19" t="s">
         <v>74</v>
@@ -3605,94 +3608,94 @@
         <v>74</v>
       </c>
       <c r="S19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA19" t="s">
         <v>74</v>
       </c>
       <c r="AB19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG19" t="s">
         <v>74</v>
       </c>
       <c r="AH19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="s">
         <v>74</v>
       </c>
       <c r="AK19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL19" t="s">
         <v>74</v>
       </c>
       <c r="AM19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>75</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR19" t="s">
         <v>76</v>
       </c>
-      <c r="AO19" t="s">
+      <c r="AS19" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT19" t="s">
         <v>76</v>
       </c>
-      <c r="AP19" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS19" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>75</v>
-      </c>
       <c r="AU19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AV19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AW19" t="s">
         <v>74</v>
@@ -3701,13 +3704,13 @@
         <v>74</v>
       </c>
       <c r="AY19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AZ19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3820,7 +3823,7 @@
         <v>74</v>
       </c>
       <c r="AK20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL20" t="s">
         <v>74</v>
@@ -3847,7 +3850,7 @@
         <v>74</v>
       </c>
       <c r="AT20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU20" t="s">
         <v>74</v>
@@ -3862,13 +3865,13 @@
         <v>74</v>
       </c>
       <c r="AY20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3876,160 +3879,160 @@
         <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s">
         <v>74</v>
       </c>
       <c r="H21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K21" t="s">
         <v>74</v>
       </c>
       <c r="L21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O21" t="s">
         <v>74</v>
       </c>
       <c r="P21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R21" t="s">
         <v>74</v>
       </c>
       <c r="S21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W21" t="s">
         <v>74</v>
       </c>
       <c r="X21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z21" t="s">
         <v>74</v>
       </c>
       <c r="AA21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC21" t="s">
         <v>74</v>
       </c>
       <c r="AD21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AI21" t="s">
         <v>74</v>
       </c>
       <c r="AJ21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL21" t="s">
         <v>74</v>
       </c>
       <c r="AM21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS21" t="s">
         <v>76</v>
       </c>
-      <c r="AN21" t="s">
+      <c r="AT21" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU21" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV21" t="s">
         <v>76</v>
       </c>
-      <c r="AO21" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP21" t="s">
-        <v>76</v>
-      </c>
-      <c r="AQ21" t="s">
-        <v>76</v>
-      </c>
-      <c r="AR21" t="s">
-        <v>76</v>
-      </c>
-      <c r="AS21" t="s">
-        <v>75</v>
-      </c>
-      <c r="AT21" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU21" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV21" t="s">
-        <v>75</v>
-      </c>
       <c r="AW21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AX21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AZ21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BA21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4040,19 +4043,19 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s">
         <v>74</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s">
         <v>74</v>
@@ -4157,22 +4160,22 @@
         <v>74</v>
       </c>
       <c r="AP22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AR22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV22" t="s">
         <v>74</v>
@@ -4181,16 +4184,16 @@
         <v>74</v>
       </c>
       <c r="AX22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sorghum_flour_percentile_classification_matrix.xlsx
+++ b/outputs/Sorghum_flour_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="77">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -244,34 +244,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>8%</t>
   </si>
 </sst>
 </file>
@@ -841,7 +814,7 @@
         <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s">
         <v>74</v>
@@ -967,13 +940,13 @@
         <v>74</v>
       </c>
       <c r="AY2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -1038,7 +1011,7 @@
         <v>74</v>
       </c>
       <c r="U3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V3" t="s">
         <v>74</v>
@@ -1050,7 +1023,7 @@
         <v>74</v>
       </c>
       <c r="Y3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z3" t="s">
         <v>74</v>
@@ -1128,13 +1101,13 @@
         <v>74</v>
       </c>
       <c r="AY3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1238,7 +1211,7 @@
         <v>74</v>
       </c>
       <c r="AH4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI4" t="s">
         <v>75</v>
@@ -1247,22 +1220,22 @@
         <v>75</v>
       </c>
       <c r="AK4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="s">
         <v>74</v>
       </c>
       <c r="AM4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AO4" t="s">
         <v>74</v>
       </c>
       <c r="AP4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AQ4" t="s">
         <v>75</v>
@@ -1289,13 +1262,13 @@
         <v>75</v>
       </c>
       <c r="AY4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="BA4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1354,7 +1327,7 @@
         <v>74</v>
       </c>
       <c r="S5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T5" t="s">
         <v>74</v>
@@ -1369,19 +1342,19 @@
         <v>74</v>
       </c>
       <c r="X5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z5" t="s">
         <v>75</v>
       </c>
       <c r="AA5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AB5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s">
         <v>75</v>
@@ -1423,7 +1396,7 @@
         <v>75</v>
       </c>
       <c r="AP5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AQ5" t="s">
         <v>74</v>
@@ -1438,7 +1411,7 @@
         <v>75</v>
       </c>
       <c r="AU5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AV5" t="s">
         <v>74</v>
@@ -1450,13 +1423,13 @@
         <v>75</v>
       </c>
       <c r="AY5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1575,7 +1548,7 @@
         <v>74</v>
       </c>
       <c r="AM6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AN6" t="s">
         <v>74</v>
@@ -1584,16 +1557,16 @@
         <v>74</v>
       </c>
       <c r="AP6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AQ6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AR6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AS6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AT6" t="s">
         <v>74</v>
@@ -1611,13 +1584,13 @@
         <v>74</v>
       </c>
       <c r="AY6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1676,7 +1649,7 @@
         <v>74</v>
       </c>
       <c r="S7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T7" t="s">
         <v>74</v>
@@ -1691,7 +1664,7 @@
         <v>75</v>
       </c>
       <c r="X7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y7" t="s">
         <v>74</v>
@@ -1700,16 +1673,16 @@
         <v>74</v>
       </c>
       <c r="AA7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AB7" t="s">
         <v>74</v>
       </c>
       <c r="AC7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AD7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AE7" t="s">
         <v>74</v>
@@ -1721,7 +1694,7 @@
         <v>75</v>
       </c>
       <c r="AH7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI7" t="s">
         <v>75</v>
@@ -1730,10 +1703,10 @@
         <v>74</v>
       </c>
       <c r="AK7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AL7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AM7" t="s">
         <v>74</v>
@@ -1772,13 +1745,13 @@
         <v>74</v>
       </c>
       <c r="AY7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1861,10 +1834,10 @@
         <v>74</v>
       </c>
       <c r="AA8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AB8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC8" t="s">
         <v>74</v>
@@ -1933,13 +1906,13 @@
         <v>74</v>
       </c>
       <c r="AY8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -2088,19 +2061,19 @@
         <v>74</v>
       </c>
       <c r="AW9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AX9" t="s">
         <v>74</v>
       </c>
       <c r="AY9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2114,13 +2087,13 @@
         <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
         <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
         <v>75</v>
@@ -2234,19 +2207,19 @@
         <v>75</v>
       </c>
       <c r="AR10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AS10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AT10" t="s">
         <v>74</v>
       </c>
       <c r="AU10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AV10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AW10" t="s">
         <v>75</v>
@@ -2255,13 +2228,13 @@
         <v>75</v>
       </c>
       <c r="AY10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2362,10 +2335,10 @@
         <v>75</v>
       </c>
       <c r="AG11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s">
         <v>74</v>
@@ -2380,22 +2353,22 @@
         <v>75</v>
       </c>
       <c r="AM11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AO11" t="s">
         <v>74</v>
       </c>
       <c r="AP11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AQ11" t="s">
         <v>75</v>
       </c>
       <c r="AR11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AS11" t="s">
         <v>74</v>
@@ -2404,25 +2377,25 @@
         <v>74</v>
       </c>
       <c r="AU11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AV11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AW11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AX11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AY11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AZ11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="BA11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2430,13 +2403,13 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>74</v>
@@ -2454,7 +2427,7 @@
         <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K12" t="s">
         <v>74</v>
@@ -2487,7 +2460,7 @@
         <v>75</v>
       </c>
       <c r="U12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V12" t="s">
         <v>74</v>
@@ -2535,13 +2508,13 @@
         <v>74</v>
       </c>
       <c r="AK12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AL12" t="s">
         <v>74</v>
       </c>
       <c r="AM12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AN12" t="s">
         <v>74</v>
@@ -2553,7 +2526,7 @@
         <v>74</v>
       </c>
       <c r="AQ12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AR12" t="s">
         <v>75</v>
@@ -2577,13 +2550,13 @@
         <v>74</v>
       </c>
       <c r="AY12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2663,13 +2636,13 @@
         <v>74</v>
       </c>
       <c r="Z13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AA13" t="s">
         <v>75</v>
       </c>
       <c r="AB13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC13" t="s">
         <v>74</v>
@@ -2681,22 +2654,22 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="s">
         <v>75</v>
       </c>
       <c r="AI13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AJ13" t="s">
         <v>74</v>
       </c>
       <c r="AK13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AL13" t="s">
         <v>74</v>
@@ -2711,10 +2684,10 @@
         <v>74</v>
       </c>
       <c r="AP13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AQ13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AR13" t="s">
         <v>74</v>
@@ -2738,13 +2711,13 @@
         <v>74</v>
       </c>
       <c r="AY13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="BA13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2839,16 +2812,16 @@
         <v>74</v>
       </c>
       <c r="AE14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AF14" t="s">
         <v>75</v>
       </c>
       <c r="AG14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI14" t="s">
         <v>75</v>
@@ -2860,16 +2833,16 @@
         <v>75</v>
       </c>
       <c r="AL14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AM14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AN14" t="s">
         <v>75</v>
       </c>
       <c r="AO14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AP14" t="s">
         <v>74</v>
@@ -2899,13 +2872,13 @@
         <v>74</v>
       </c>
       <c r="AY14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -2958,7 +2931,7 @@
         <v>74</v>
       </c>
       <c r="Q15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R15" t="s">
         <v>75</v>
@@ -2967,25 +2940,25 @@
         <v>75</v>
       </c>
       <c r="T15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V15" t="s">
         <v>75</v>
       </c>
       <c r="W15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X15" t="s">
         <v>74</v>
       </c>
       <c r="Y15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AA15" t="s">
         <v>75</v>
@@ -3015,7 +2988,7 @@
         <v>74</v>
       </c>
       <c r="AJ15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AK15" t="s">
         <v>74</v>
@@ -3036,7 +3009,7 @@
         <v>75</v>
       </c>
       <c r="AQ15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AR15" t="s">
         <v>74</v>
@@ -3060,13 +3033,13 @@
         <v>74</v>
       </c>
       <c r="AY15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="BA15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3077,10 +3050,10 @@
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
         <v>74</v>
@@ -3146,7 +3119,7 @@
         <v>74</v>
       </c>
       <c r="Z16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AA16" t="s">
         <v>74</v>
@@ -3164,7 +3137,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG16" t="s">
         <v>74</v>
@@ -3212,7 +3185,7 @@
         <v>75</v>
       </c>
       <c r="AV16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AW16" t="s">
         <v>75</v>
@@ -3221,13 +3194,13 @@
         <v>74</v>
       </c>
       <c r="AY16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3280,7 +3253,7 @@
         <v>74</v>
       </c>
       <c r="Q17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R17" t="s">
         <v>74</v>
@@ -3355,16 +3328,16 @@
         <v>74</v>
       </c>
       <c r="AP17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AQ17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AR17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AS17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AT17" t="s">
         <v>75</v>
@@ -3373,22 +3346,22 @@
         <v>75</v>
       </c>
       <c r="AV17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AW17" t="s">
         <v>74</v>
       </c>
       <c r="AX17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AY17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3426,7 +3399,7 @@
         <v>74</v>
       </c>
       <c r="L18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M18" t="s">
         <v>75</v>
@@ -3441,7 +3414,7 @@
         <v>75</v>
       </c>
       <c r="Q18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R18" t="s">
         <v>75</v>
@@ -3483,7 +3456,7 @@
         <v>75</v>
       </c>
       <c r="AE18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AF18" t="s">
         <v>75</v>
@@ -3507,7 +3480,7 @@
         <v>74</v>
       </c>
       <c r="AM18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AN18" t="s">
         <v>75</v>
@@ -3516,7 +3489,7 @@
         <v>74</v>
       </c>
       <c r="AP18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AQ18" t="s">
         <v>74</v>
@@ -3528,7 +3501,7 @@
         <v>75</v>
       </c>
       <c r="AT18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AU18" t="s">
         <v>75</v>
@@ -3540,16 +3513,16 @@
         <v>74</v>
       </c>
       <c r="AX18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AY18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AZ18" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="BA18" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3662,7 +3635,7 @@
         <v>74</v>
       </c>
       <c r="AK19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AL19" t="s">
         <v>74</v>
@@ -3671,10 +3644,10 @@
         <v>75</v>
       </c>
       <c r="AN19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AO19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AP19" t="s">
         <v>75</v>
@@ -3683,19 +3656,19 @@
         <v>74</v>
       </c>
       <c r="AR19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AS19" t="s">
         <v>75</v>
       </c>
       <c r="AT19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AU19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AV19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AW19" t="s">
         <v>74</v>
@@ -3704,13 +3677,13 @@
         <v>74</v>
       </c>
       <c r="AY19" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AZ19" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="BA19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3823,7 +3796,7 @@
         <v>74</v>
       </c>
       <c r="AK20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AL20" t="s">
         <v>74</v>
@@ -3850,7 +3823,7 @@
         <v>74</v>
       </c>
       <c r="AT20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AU20" t="s">
         <v>74</v>
@@ -3865,13 +3838,13 @@
         <v>74</v>
       </c>
       <c r="AY20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3975,7 +3948,7 @@
         <v>75</v>
       </c>
       <c r="AH21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s">
         <v>74</v>
@@ -3990,25 +3963,25 @@
         <v>74</v>
       </c>
       <c r="AM21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AN21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AO21" t="s">
         <v>74</v>
       </c>
       <c r="AP21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AQ21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AR21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AS21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AT21" t="s">
         <v>74</v>
@@ -4017,22 +3990,22 @@
         <v>74</v>
       </c>
       <c r="AV21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AW21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AX21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AY21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AZ21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="BA21" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4043,13 +4016,13 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F22" t="s">
         <v>74</v>
@@ -4160,22 +4133,22 @@
         <v>74</v>
       </c>
       <c r="AP22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AQ22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AR22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AS22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AT22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AU22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AV22" t="s">
         <v>74</v>
@@ -4184,16 +4157,16 @@
         <v>74</v>
       </c>
       <c r="AX22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AY22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="BA22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sorghum_flour_percentile_classification_matrix.xlsx
+++ b/outputs/Sorghum_flour_percentile_classification_matrix.xlsx
@@ -241,7 +241,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
